--- a/Unity/Assets/Config/Excel/PetConfig.xlsx
+++ b/Unity/Assets/Config/Excel/PetConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB6D7F4-E830-47FE-9096-FC228BFA8083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E10F418-2129-40CE-AD6F-2FAF1A861993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PetProto" sheetId="1" r:id="rId1"/>
@@ -829,18 +829,12 @@
     <t>2301010,0.5;2303140,0.152303090,0.15</t>
   </si>
   <si>
-    <t>螃蟹护卫</t>
-  </si>
-  <si>
     <t>0,90,250,50,0</t>
   </si>
   <si>
     <t>2301011,0.5;2301013,0.3;2303150,0.15</t>
   </si>
   <si>
-    <t>猛虎</t>
-  </si>
-  <si>
     <t>2301012,0.5;2302016,0.3;2303160,0.15</t>
   </si>
   <si>
@@ -884,9 +878,6 @@
   </si>
   <si>
     <t>2301018,0.5;2302005,0.3;2303220,0.15</t>
-  </si>
-  <si>
-    <t>雪狼</t>
   </si>
   <si>
     <t>0,80,250,45,0</t>
@@ -1023,6 +1014,17 @@
   <si>
     <t>软泥怪</t>
     <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰狼</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>山虎</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>青甲护卫</t>
   </si>
 </sst>
 </file>
@@ -4531,7 +4533,7 @@
         <v>310101</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E9" s="8">
         <v>310101</v>
@@ -10075,7 +10077,7 @@
         <v>330101</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>156</v>
+        <v>220</v>
       </c>
       <c r="E23" s="8">
         <v>330101</v>
@@ -10087,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I23" s="9">
         <v>0</v>
@@ -10240,7 +10242,7 @@
         <v>2301012</v>
       </c>
       <c r="BG23" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BH23" s="15">
         <v>330101</v>
@@ -10471,7 +10473,7 @@
         <v>330102</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="E24" s="8">
         <v>330102</v>
@@ -10636,7 +10638,7 @@
         <v>2301006</v>
       </c>
       <c r="BG24" s="14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="BH24" s="15">
         <v>330102</v>
@@ -10867,7 +10869,7 @@
         <v>330103</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E25" s="8">
         <v>330103</v>
@@ -11032,7 +11034,7 @@
         <v>2301001</v>
       </c>
       <c r="BG25" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="BH25" s="15">
         <v>330103</v>
@@ -11263,7 +11265,7 @@
         <v>330104</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E26" s="8">
         <v>330104</v>
@@ -11428,7 +11430,7 @@
         <v>2301005</v>
       </c>
       <c r="BG26" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="BH26" s="15">
         <v>330104</v>
@@ -11659,7 +11661,7 @@
         <v>330105</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E27" s="8">
         <v>330105</v>
@@ -11824,7 +11826,7 @@
         <v>2301006</v>
       </c>
       <c r="BG27" s="14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="BH27" s="15">
         <v>330105</v>
@@ -12055,7 +12057,7 @@
         <v>330106</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E28" s="8">
         <v>330106</v>
@@ -12067,7 +12069,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I28" s="9">
         <v>0</v>
@@ -12220,7 +12222,7 @@
         <v>2301007</v>
       </c>
       <c r="BG28" s="14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="BH28" s="15">
         <v>330106</v>
@@ -12451,7 +12453,7 @@
         <v>330107</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E29" s="8">
         <v>330107</v>
@@ -12463,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I29" s="9">
         <v>0</v>
@@ -12616,7 +12618,7 @@
         <v>2301008</v>
       </c>
       <c r="BG29" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="BH29" s="15">
         <v>330107</v>
@@ -12847,7 +12849,7 @@
         <v>340101</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E30" s="8">
         <v>340101</v>
@@ -12859,7 +12861,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I30" s="9">
         <v>0</v>
@@ -13012,7 +13014,7 @@
         <v>2301009</v>
       </c>
       <c r="BG30" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="BH30" s="15">
         <v>340101</v>
@@ -13243,7 +13245,7 @@
         <v>340102</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="E31" s="8">
         <v>340102</v>
@@ -13255,7 +13257,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I31" s="9">
         <v>0</v>
@@ -13408,7 +13410,7 @@
         <v>2301010</v>
       </c>
       <c r="BG31" s="14" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="BH31" s="15">
         <v>340102</v>
@@ -13639,7 +13641,7 @@
         <v>340103</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E32" s="8">
         <v>340103</v>
@@ -13651,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I32" s="9">
         <v>0</v>
@@ -13804,7 +13806,7 @@
         <v>2301001</v>
       </c>
       <c r="BG32" s="14" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="BH32" s="15">
         <v>340103</v>
@@ -14035,7 +14037,7 @@
         <v>340104</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E33" s="8">
         <v>340104</v>
@@ -14200,7 +14202,7 @@
         <v>2301004</v>
       </c>
       <c r="BG33" s="14" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BH33" s="15">
         <v>340104</v>
@@ -14431,7 +14433,7 @@
         <v>340105</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E34" s="8">
         <v>340105</v>
@@ -14596,7 +14598,7 @@
         <v>2301011</v>
       </c>
       <c r="BG34" s="14" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BH34" s="15">
         <v>340105</v>
@@ -14827,7 +14829,7 @@
         <v>340106</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E35" s="8">
         <v>340106</v>
@@ -14839,7 +14841,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I35" s="9">
         <v>0</v>
@@ -14992,7 +14994,7 @@
         <v>2301003</v>
       </c>
       <c r="BG35" s="14" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="BH35" s="15">
         <v>340106</v>
@@ -15223,7 +15225,7 @@
         <v>340107</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E36" s="8">
         <v>340107</v>
@@ -15388,7 +15390,7 @@
         <v>2301010</v>
       </c>
       <c r="BG36" s="14" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="BH36" s="15">
         <v>340107</v>
@@ -15619,7 +15621,7 @@
         <v>350101</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E37" s="8">
         <v>350101</v>
@@ -15631,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I37" s="9">
         <v>0</v>
@@ -15784,7 +15786,7 @@
         <v>2301013</v>
       </c>
       <c r="BG37" s="14" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="BH37" s="15">
         <v>350101</v>
@@ -16015,7 +16017,7 @@
         <v>350102</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E38" s="8">
         <v>350102</v>
@@ -16180,7 +16182,7 @@
         <v>2301014</v>
       </c>
       <c r="BG38" s="14" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="BH38" s="15">
         <v>350102</v>
@@ -16411,7 +16413,7 @@
         <v>350103</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E39" s="8">
         <v>350103</v>
@@ -16576,7 +16578,7 @@
         <v>2301013</v>
       </c>
       <c r="BG39" s="14" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="BH39" s="15">
         <v>350103</v>
@@ -16807,7 +16809,7 @@
         <v>350104</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E40" s="8">
         <v>350104</v>
@@ -16819,7 +16821,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I40" s="9">
         <v>0</v>
@@ -16972,7 +16974,7 @@
         <v>2301008</v>
       </c>
       <c r="BG40" s="14" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="BH40" s="15">
         <v>350104</v>
@@ -17203,7 +17205,7 @@
         <v>350105</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E41" s="8">
         <v>350105</v>
@@ -17215,7 +17217,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I41" s="9">
         <v>0</v>
@@ -17368,7 +17370,7 @@
         <v>2301010</v>
       </c>
       <c r="BG41" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="BH41" s="15">
         <v>350105</v>
@@ -17599,7 +17601,7 @@
         <v>350106</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E42" s="8">
         <v>350106</v>
@@ -17611,7 +17613,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I42" s="9">
         <v>0</v>
@@ -17764,7 +17766,7 @@
         <v>2301011</v>
       </c>
       <c r="BG42" s="14" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="BH42" s="15">
         <v>350106</v>
@@ -17995,7 +17997,7 @@
         <v>400001</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E43" s="8">
         <v>400001</v>
@@ -18007,7 +18009,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I43" s="9">
         <v>0</v>
@@ -18160,7 +18162,7 @@
         <v>2301002</v>
       </c>
       <c r="BG43" s="14" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="BH43" s="15">
         <v>400001</v>
@@ -18391,7 +18393,7 @@
         <v>400002</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E44" s="8">
         <v>400002</v>
@@ -18556,7 +18558,7 @@
         <v>2301008</v>
       </c>
       <c r="BG44" s="14" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="BH44" s="15">
         <v>400002</v>
@@ -18787,7 +18789,7 @@
         <v>400003</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E45" s="8">
         <v>400003</v>
@@ -18799,7 +18801,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I45" s="9">
         <v>0</v>
@@ -18952,7 +18954,7 @@
         <v>2301006</v>
       </c>
       <c r="BG45" s="14" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="BH45" s="15">
         <v>400003</v>
@@ -19183,7 +19185,7 @@
         <v>400004</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E46" s="8">
         <v>400004</v>
@@ -19195,7 +19197,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I46" s="9">
         <v>0</v>
@@ -19348,7 +19350,7 @@
         <v>2301006</v>
       </c>
       <c r="BG46" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="BH46" s="15">
         <v>400004</v>
@@ -19579,7 +19581,7 @@
         <v>400005</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E47" s="8">
         <v>400005</v>
@@ -19591,7 +19593,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I47" s="9">
         <v>0</v>
@@ -19744,7 +19746,7 @@
         <v>2301010</v>
       </c>
       <c r="BG47" s="14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="BH47" s="15">
         <v>400005</v>
@@ -19975,7 +19977,7 @@
         <v>400006</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E48" s="8">
         <v>400006</v>
@@ -19987,7 +19989,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I48" s="9">
         <v>0</v>
@@ -20140,7 +20142,7 @@
         <v>2301011</v>
       </c>
       <c r="BG48" s="14" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="BH48" s="15">
         <v>400006</v>
@@ -20371,7 +20373,7 @@
         <v>400007</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E49" s="8">
         <v>400007</v>
@@ -20383,7 +20385,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I49" s="9">
         <v>0</v>
@@ -20536,7 +20538,7 @@
         <v>2301002</v>
       </c>
       <c r="BG49" s="14" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BH49" s="15">
         <v>400007</v>
@@ -20767,7 +20769,7 @@
         <v>400008</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E50" s="8">
         <v>400008</v>
@@ -20932,7 +20934,7 @@
         <v>2301012</v>
       </c>
       <c r="BG50" s="14" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="BH50" s="15">
         <v>400008</v>

--- a/Unity/Assets/Config/Excel/PetConfig.xlsx
+++ b/Unity/Assets/Config/Excel/PetConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E10F418-2129-40CE-AD6F-2FAF1A861993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC61899-DF21-49EF-AED8-84B4AFCB6588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PetProto" sheetId="1" r:id="rId1"/>
@@ -760,9 +760,6 @@
     <t>2301013,0.5;2301007,0.15;2303040,0.15</t>
   </si>
   <si>
-    <t>山贼</t>
-  </si>
-  <si>
     <t>2301012,0.3;2303050,0.15</t>
   </si>
   <si>
@@ -1025,6 +1022,10 @@
   </si>
   <si>
     <t>青甲护卫</t>
+  </si>
+  <si>
+    <t>绿石怪</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4533,7 +4534,7 @@
         <v>310101</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E9" s="8">
         <v>310101</v>
@@ -6117,7 +6118,7 @@
         <v>310105</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>133</v>
+        <v>220</v>
       </c>
       <c r="E13" s="8">
         <v>310105</v>
@@ -6282,7 +6283,7 @@
         <v>2301010</v>
       </c>
       <c r="BG13" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BH13" s="15">
         <v>310105</v>
@@ -6513,7 +6514,7 @@
         <v>310106</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E14" s="8">
         <v>310106</v>
@@ -6525,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I14" s="9">
         <v>0</v>
@@ -6678,7 +6679,7 @@
         <v>2301001</v>
       </c>
       <c r="BG14" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BH14" s="15">
         <v>310106</v>
@@ -6909,7 +6910,7 @@
         <v>310107</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E15" s="8">
         <v>310107</v>
@@ -6921,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I15" s="9">
         <v>0</v>
@@ -7074,7 +7075,7 @@
         <v>2301018</v>
       </c>
       <c r="BG15" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BH15" s="15">
         <v>310107</v>
@@ -7305,7 +7306,7 @@
         <v>320101</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E16" s="8">
         <v>320101</v>
@@ -7317,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I16" s="9">
         <v>0</v>
@@ -7470,7 +7471,7 @@
         <v>2301008</v>
       </c>
       <c r="BG16" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH16" s="15">
         <v>320101</v>
@@ -7701,7 +7702,7 @@
         <v>320102</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E17" s="8">
         <v>320102</v>
@@ -7866,7 +7867,7 @@
         <v>2301002</v>
       </c>
       <c r="BG17" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BH17" s="15">
         <v>320102</v>
@@ -8097,7 +8098,7 @@
         <v>320103</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E18" s="8">
         <v>320103</v>
@@ -8109,7 +8110,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I18" s="9">
         <v>0</v>
@@ -8262,7 +8263,7 @@
         <v>2301009</v>
       </c>
       <c r="BG18" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BH18" s="15">
         <v>320103</v>
@@ -8493,7 +8494,7 @@
         <v>320104</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" s="8">
         <v>320104</v>
@@ -8505,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I19" s="9">
         <v>0</v>
@@ -8658,7 +8659,7 @@
         <v>2301011</v>
       </c>
       <c r="BG19" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BH19" s="15">
         <v>320104</v>
@@ -8889,7 +8890,7 @@
         <v>320105</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E20" s="8">
         <v>320105</v>
@@ -9054,7 +9055,7 @@
         <v>2301020</v>
       </c>
       <c r="BG20" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BH20" s="15">
         <v>320105</v>
@@ -9285,7 +9286,7 @@
         <v>320106</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E21" s="8">
         <v>320106</v>
@@ -9297,7 +9298,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I21" s="9">
         <v>0</v>
@@ -9450,7 +9451,7 @@
         <v>2301005</v>
       </c>
       <c r="BG21" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BH21" s="15">
         <v>320106</v>
@@ -9681,7 +9682,7 @@
         <v>320107</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E22" s="8">
         <v>320107</v>
@@ -9846,7 +9847,7 @@
         <v>2301015</v>
       </c>
       <c r="BG22" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BH22" s="15">
         <v>320107</v>
@@ -10077,7 +10078,7 @@
         <v>330101</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E23" s="8">
         <v>330101</v>
@@ -10089,7 +10090,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I23" s="9">
         <v>0</v>
@@ -10242,7 +10243,7 @@
         <v>2301012</v>
       </c>
       <c r="BG23" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BH23" s="15">
         <v>330101</v>
@@ -10473,7 +10474,7 @@
         <v>330102</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E24" s="8">
         <v>330102</v>
@@ -10485,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I24" s="9">
         <v>0</v>
@@ -10638,7 +10639,7 @@
         <v>2301006</v>
       </c>
       <c r="BG24" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BH24" s="15">
         <v>330102</v>
@@ -10869,7 +10870,7 @@
         <v>330103</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E25" s="8">
         <v>330103</v>
@@ -10881,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I25" s="9">
         <v>0</v>
@@ -11034,7 +11035,7 @@
         <v>2301001</v>
       </c>
       <c r="BG25" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BH25" s="15">
         <v>330103</v>
@@ -11265,7 +11266,7 @@
         <v>330104</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E26" s="8">
         <v>330104</v>
@@ -11430,7 +11431,7 @@
         <v>2301005</v>
       </c>
       <c r="BG26" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BH26" s="15">
         <v>330104</v>
@@ -11661,7 +11662,7 @@
         <v>330105</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E27" s="8">
         <v>330105</v>
@@ -11826,7 +11827,7 @@
         <v>2301006</v>
       </c>
       <c r="BG27" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BH27" s="15">
         <v>330105</v>
@@ -12057,7 +12058,7 @@
         <v>330106</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E28" s="8">
         <v>330106</v>
@@ -12069,7 +12070,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I28" s="9">
         <v>0</v>
@@ -12222,7 +12223,7 @@
         <v>2301007</v>
       </c>
       <c r="BG28" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="BH28" s="15">
         <v>330106</v>
@@ -12453,7 +12454,7 @@
         <v>330107</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E29" s="8">
         <v>330107</v>
@@ -12465,7 +12466,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I29" s="9">
         <v>0</v>
@@ -12618,7 +12619,7 @@
         <v>2301008</v>
       </c>
       <c r="BG29" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BH29" s="15">
         <v>330107</v>
@@ -12849,7 +12850,7 @@
         <v>340101</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E30" s="8">
         <v>340101</v>
@@ -12861,7 +12862,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I30" s="9">
         <v>0</v>
@@ -13014,7 +13015,7 @@
         <v>2301009</v>
       </c>
       <c r="BG30" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BH30" s="15">
         <v>340101</v>
@@ -13245,7 +13246,7 @@
         <v>340102</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E31" s="8">
         <v>340102</v>
@@ -13257,7 +13258,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I31" s="9">
         <v>0</v>
@@ -13410,7 +13411,7 @@
         <v>2301010</v>
       </c>
       <c r="BG31" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BH31" s="15">
         <v>340102</v>
@@ -13641,7 +13642,7 @@
         <v>340103</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E32" s="8">
         <v>340103</v>
@@ -13653,7 +13654,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I32" s="9">
         <v>0</v>
@@ -13806,7 +13807,7 @@
         <v>2301001</v>
       </c>
       <c r="BG32" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BH32" s="15">
         <v>340103</v>
@@ -14037,7 +14038,7 @@
         <v>340104</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E33" s="8">
         <v>340104</v>
@@ -14202,7 +14203,7 @@
         <v>2301004</v>
       </c>
       <c r="BG33" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="BH33" s="15">
         <v>340104</v>
@@ -14433,7 +14434,7 @@
         <v>340105</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E34" s="8">
         <v>340105</v>
@@ -14445,7 +14446,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I34" s="9">
         <v>0</v>
@@ -14598,7 +14599,7 @@
         <v>2301011</v>
       </c>
       <c r="BG34" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BH34" s="15">
         <v>340105</v>
@@ -14829,7 +14830,7 @@
         <v>340106</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E35" s="8">
         <v>340106</v>
@@ -14841,7 +14842,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I35" s="9">
         <v>0</v>
@@ -14994,7 +14995,7 @@
         <v>2301003</v>
       </c>
       <c r="BG35" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BH35" s="15">
         <v>340106</v>
@@ -15225,7 +15226,7 @@
         <v>340107</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E36" s="8">
         <v>340107</v>
@@ -15237,7 +15238,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I36" s="9">
         <v>0</v>
@@ -15390,7 +15391,7 @@
         <v>2301010</v>
       </c>
       <c r="BG36" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BH36" s="15">
         <v>340107</v>
@@ -15621,7 +15622,7 @@
         <v>350101</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E37" s="8">
         <v>350101</v>
@@ -15633,7 +15634,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I37" s="9">
         <v>0</v>
@@ -15786,7 +15787,7 @@
         <v>2301013</v>
       </c>
       <c r="BG37" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BH37" s="15">
         <v>350101</v>
@@ -16017,7 +16018,7 @@
         <v>350102</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E38" s="8">
         <v>350102</v>
@@ -16029,7 +16030,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I38" s="9">
         <v>0</v>
@@ -16182,7 +16183,7 @@
         <v>2301014</v>
       </c>
       <c r="BG38" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BH38" s="15">
         <v>350102</v>
@@ -16413,7 +16414,7 @@
         <v>350103</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E39" s="8">
         <v>350103</v>
@@ -16578,7 +16579,7 @@
         <v>2301013</v>
       </c>
       <c r="BG39" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BH39" s="15">
         <v>350103</v>
@@ -16809,7 +16810,7 @@
         <v>350104</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E40" s="8">
         <v>350104</v>
@@ -16821,7 +16822,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I40" s="9">
         <v>0</v>
@@ -16974,7 +16975,7 @@
         <v>2301008</v>
       </c>
       <c r="BG40" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BH40" s="15">
         <v>350104</v>
@@ -17205,7 +17206,7 @@
         <v>350105</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E41" s="8">
         <v>350105</v>
@@ -17217,7 +17218,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I41" s="9">
         <v>0</v>
@@ -17370,7 +17371,7 @@
         <v>2301010</v>
       </c>
       <c r="BG41" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BH41" s="15">
         <v>350105</v>
@@ -17601,7 +17602,7 @@
         <v>350106</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E42" s="8">
         <v>350106</v>
@@ -17613,7 +17614,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I42" s="9">
         <v>0</v>
@@ -17766,7 +17767,7 @@
         <v>2301011</v>
       </c>
       <c r="BG42" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BH42" s="15">
         <v>350106</v>
@@ -17997,7 +17998,7 @@
         <v>400001</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E43" s="8">
         <v>400001</v>
@@ -18009,7 +18010,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I43" s="9">
         <v>0</v>
@@ -18162,7 +18163,7 @@
         <v>2301002</v>
       </c>
       <c r="BG43" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BH43" s="15">
         <v>400001</v>
@@ -18393,7 +18394,7 @@
         <v>400002</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E44" s="8">
         <v>400002</v>
@@ -18558,7 +18559,7 @@
         <v>2301008</v>
       </c>
       <c r="BG44" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BH44" s="15">
         <v>400002</v>
@@ -18789,7 +18790,7 @@
         <v>400003</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E45" s="8">
         <v>400003</v>
@@ -18801,7 +18802,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I45" s="9">
         <v>0</v>
@@ -18954,7 +18955,7 @@
         <v>2301006</v>
       </c>
       <c r="BG45" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BH45" s="15">
         <v>400003</v>
@@ -19185,7 +19186,7 @@
         <v>400004</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E46" s="8">
         <v>400004</v>
@@ -19197,7 +19198,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I46" s="9">
         <v>0</v>
@@ -19350,7 +19351,7 @@
         <v>2301006</v>
       </c>
       <c r="BG46" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BH46" s="15">
         <v>400004</v>
@@ -19581,7 +19582,7 @@
         <v>400005</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E47" s="8">
         <v>400005</v>
@@ -19593,7 +19594,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I47" s="9">
         <v>0</v>
@@ -19746,7 +19747,7 @@
         <v>2301010</v>
       </c>
       <c r="BG47" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BH47" s="15">
         <v>400005</v>
@@ -19977,7 +19978,7 @@
         <v>400006</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E48" s="8">
         <v>400006</v>
@@ -19989,7 +19990,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I48" s="9">
         <v>0</v>
@@ -20142,7 +20143,7 @@
         <v>2301011</v>
       </c>
       <c r="BG48" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BH48" s="15">
         <v>400006</v>
@@ -20373,7 +20374,7 @@
         <v>400007</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E49" s="8">
         <v>400007</v>
@@ -20385,7 +20386,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I49" s="9">
         <v>0</v>
@@ -20538,7 +20539,7 @@
         <v>2301002</v>
       </c>
       <c r="BG49" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BH49" s="15">
         <v>400007</v>
@@ -20769,7 +20770,7 @@
         <v>400008</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E50" s="8">
         <v>400008</v>
@@ -20934,7 +20935,7 @@
         <v>2301012</v>
       </c>
       <c r="BG50" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="BH50" s="15">
         <v>400008</v>
